--- a/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
+++ b/modulos/plan-anual/ASIGNACION DE COMPETENCIAS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manu/Desktop/GAV-APP-AKC-main/modulos/plan-anual/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55b6a939d4276db6/INFORMES AKC/CICLO 26-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6D2FA84-B281-6542-9ADC-4B653BAE5D11}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{4681491B-5DA5-504A-8D59-CA9E43B0ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{914884E5-ECDF-FA4A-89CA-EFA33A6755B4}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,10 +165,6 @@
   </si>
   <si>
     <t>SEDE
-Tlaxcala Tlaxcala</t>
-  </si>
-  <si>
-    <t>SEDE
 CDMX</t>
   </si>
   <si>
@@ -212,9 +208,6 @@
     <t>MIKULAK INVITATIONAL CUP 27</t>
   </si>
   <si>
-    <t>COPA ACTION GYM o CDI 26</t>
-  </si>
-  <si>
     <t>JUEGOS CONADE ON 27</t>
   </si>
   <si>
@@ -229,6 +222,13 @@
   </si>
   <si>
     <t>CONTROL INTERNO</t>
+  </si>
+  <si>
+    <t>COPA CDI 26</t>
+  </si>
+  <si>
+    <t>SEDE
+Ciudad de Mexico Centro Deportivo Israelita</t>
   </si>
 </sst>
 </file>
@@ -713,7 +713,7 @@
   <sheetFormatPr defaultColWidth="9.01171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.76171875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.89453125" style="1" customWidth="1"/>
     <col min="3" max="14" width="12.375" style="1" customWidth="1"/>
     <col min="15" max="15" width="15.19921875" style="1" customWidth="1"/>
     <col min="16" max="16384" width="9.01171875" style="1"/>
@@ -727,25 +727,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>35</v>
@@ -754,13 +754,13 @@
         <v>36</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>37</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>2</v>
@@ -770,40 +770,40 @@
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O2" s="4"/>
     </row>
@@ -947,7 +947,7 @@
         <v>5</v>
       </c>
       <c r="O5" s="6">
-        <f>COUNTIF(C5:N5,"SI")/9</f>
+        <f t="shared" ref="O5:O17" si="0">COUNTIF(C5:N5,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -995,7 +995,7 @@
         <v>5</v>
       </c>
       <c r="O6" s="6">
-        <f>COUNTIF(C6:N6,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
         <v>5</v>
       </c>
       <c r="O7" s="6">
-        <f>COUNTIF(C7:N7,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
         <v>5</v>
       </c>
       <c r="O8" s="6">
-        <f>COUNTIF(C8:N8,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -1139,7 +1139,7 @@
         <v>5</v>
       </c>
       <c r="O9" s="6">
-        <f>COUNTIF(C9:N9,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
         <v>5</v>
       </c>
       <c r="O10" s="6">
-        <f>COUNTIF(C10:N10,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
         <v>5</v>
       </c>
       <c r="O11" s="6">
-        <f>COUNTIF(C11:N11,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -1283,7 +1283,7 @@
         <v>5</v>
       </c>
       <c r="O12" s="6">
-        <f>COUNTIF(C12:N12,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
         <v>5</v>
       </c>
       <c r="O13" s="6">
-        <f>COUNTIF(C13:N13,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         <v>5</v>
       </c>
       <c r="O14" s="6">
-        <f>COUNTIF(C14:N14,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="O15" s="6">
-        <f>COUNTIF(C15:N15,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
         <v>5</v>
       </c>
       <c r="O16" s="6">
-        <f>COUNTIF(C16:N16,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="O17" s="6">
-        <f>COUNTIF(C17:N17,"SI")/9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
         <v>9</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>4</v>
@@ -1859,7 +1859,7 @@
         <v>4</v>
       </c>
       <c r="O24" s="6">
-        <f>COUNTIF(C24:N24,"SI")/12</f>
+        <f>COUNTIF(C24:N24,"SI")/11</f>
         <v>1</v>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
         <v>9</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>4</v>
@@ -1907,7 +1907,7 @@
         <v>5</v>
       </c>
       <c r="O25" s="6">
-        <f>COUNTIF(C25:N25,"SI")/11</f>
+        <f>COUNTIF(C25:N25,"SI")/10</f>
         <v>1</v>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
         <v>9</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>4</v>
@@ -1955,7 +1955,7 @@
         <v>4</v>
       </c>
       <c r="O26" s="6">
-        <f>COUNTIF(C26:N26,"SI")/10</f>
+        <f>COUNTIF(C26:N26,"SI")/9</f>
         <v>1</v>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
         <v>9</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>4</v>
@@ -2003,7 +2003,7 @@
         <v>4</v>
       </c>
       <c r="O27" s="6">
-        <f>COUNTIF(C27:N27,"SI")/12</f>
+        <f>COUNTIF(C27:N27,"SI")/11</f>
         <v>1</v>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>4</v>
@@ -2051,7 +2051,7 @@
         <v>4</v>
       </c>
       <c r="O28" s="6">
-        <f>COUNTIF(C28:N28,"SI")/12</f>
+        <f>COUNTIF(C28:N28,"SI")/11</f>
         <v>1</v>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>4</v>
@@ -2099,7 +2099,7 @@
         <v>4</v>
       </c>
       <c r="O29" s="6">
-        <f>COUNTIF(C29:N29,"SI")/12</f>
+        <f>COUNTIF(C29:N29,"SI")/11</f>
         <v>1</v>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>4</v>
@@ -2147,7 +2147,7 @@
         <v>4</v>
       </c>
       <c r="O30" s="6">
-        <f>COUNTIF(C30:N30,"SI")/12</f>
+        <f>COUNTIF(C30:N30,"SI")/11</f>
         <v>1</v>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
         <v>38</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>4</v>
@@ -2195,7 +2195,7 @@
         <v>5</v>
       </c>
       <c r="O31" s="6">
-        <f>COUNTIF(C31:N31,"SI")/11</f>
+        <f>COUNTIF(C31:N31,"SI")/10</f>
         <v>1</v>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
         <v>38</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>4</v>
@@ -2291,7 +2291,7 @@
         <v>5</v>
       </c>
       <c r="O33" s="6">
-        <f>COUNTIF(C33:N33,"SI")/11</f>
+        <f>COUNTIF(C33:N33,"SI")/10</f>
         <v>1</v>
       </c>
     </row>
